--- a/input/Studies/MEET2/Compressor.xlsx
+++ b/input/Studies/MEET2/Compressor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MEET2_main\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BAACED-3340-4CEF-9529-3CD595568908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48C04CD-F929-4DC8-A04A-E7D0E82506EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="694" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="694" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -970,13 +970,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -984,7 +984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -992,7 +992,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>137</v>
       </c>
@@ -1016,16 +1016,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1059,11 +1059,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
     </row>
@@ -1075,21 +1075,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37528EC0-9D38-4387-9F22-FC0929712721}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="15.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="9" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="9" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1161,60 +1161,60 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BC14"/>
-  <sheetFormatPr defaultColWidth="39.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="39.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="60.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7265625" customWidth="1"/>
+    <col min="10" max="10" width="22.54296875" customWidth="1"/>
+    <col min="11" max="11" width="60.453125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="15.42578125" customWidth="1"/>
-    <col min="23" max="23" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.453125" customWidth="1"/>
+    <col min="23" max="23" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="28.54296875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.81640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="21" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="34.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="32.54296875" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="33" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="34.453125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="48" max="51" width="38" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="16" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="28" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="28" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>41</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -3575,14 +3575,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62357F51-8B1A-4F0A-A196-97EDC5E724F9}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3613,18 +3613,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4780323A-AA8D-4192-A121-B75F269C58B7}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G2" s="17"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -3857,15 +3857,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4B5BD6E-76BA-47A4-8123-097FFE5BFF7D}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -3932,12 +3932,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -3945,7 +3945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -4001,12 +4001,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68AB5E8D-A6F3-4D07-A645-8147E696BBBE}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>

--- a/input/Studies/MEET2/Compressor.xlsx
+++ b/input/Studies/MEET2/Compressor.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC14"/>
+  <dimension ref="A1:BD14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="39.54296875" defaultRowHeight="14.5"/>
   <cols>
     <col width="11.453125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1241,6 +1241,11 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1429,6 +1434,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1617,6 +1625,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1805,6 +1816,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1993,6 +2007,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2181,6 +2198,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2369,6 +2389,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2557,6 +2580,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2745,6 +2771,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2933,6 +2962,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3121,6 +3153,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3309,6 +3344,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3497,6 +3535,9 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BD13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3684,6 +3725,9 @@
         <is>
           <t>ts_compressor</t>
         </is>
+      </c>
+      <c r="BD14" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
